--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/todos.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/todos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="licencia-de-software todos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="licencia-de-software todos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21658,7 +21658,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22268,7 +22268,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23305,7 +23305,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23427,7 +23427,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23740,7 +23740,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24167,7 +24167,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24293,7 +24293,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25818,7 +25818,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27362,7 +27362,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -28270,7 +28270,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28331,7 +28331,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28880,7 +28880,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29566,7 +29566,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -30352,7 +30352,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31816,7 +31816,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31831,7 +31831,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -33044,7 +33044,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33471,7 +33471,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -34222,7 +34222,7 @@
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34699,7 +34699,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34760,7 +34760,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -35004,7 +35004,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35065,7 +35065,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35370,7 +35370,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35614,7 +35614,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -36224,7 +36224,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36544,7 +36544,7 @@
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36960,7 +36960,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37097,7 +37097,7 @@
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37635,7 +37635,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37818,7 +37818,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37833,7 +37833,7 @@
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
@@ -38081,7 +38081,7 @@
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
@@ -38268,7 +38268,7 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
@@ -38562,7 +38562,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39477,7 +39477,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39965,7 +39965,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40026,7 +40026,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -40087,7 +40087,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40453,7 +40453,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -42226,7 +42226,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42363,7 +42363,7 @@
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L685" t="inlineStr">
@@ -43999,7 +43999,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44548,7 +44548,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44792,7 +44792,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44975,7 +44975,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45036,7 +45036,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45768,7 +45768,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45951,7 +45951,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -46378,7 +46378,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46881,7 +46881,7 @@
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L759" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -47434,7 +47434,7 @@
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
@@ -47667,7 +47667,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47789,7 +47789,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -48353,7 +48353,7 @@
       </c>
       <c r="K783" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L783" t="inlineStr">
@@ -48418,7 +48418,7 @@
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
@@ -48483,7 +48483,7 @@
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
@@ -49021,7 +49021,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -49753,7 +49753,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -50180,7 +50180,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50729,7 +50729,7 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -50927,7 +50927,7 @@
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
@@ -50992,7 +50992,7 @@
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
@@ -51164,7 +51164,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -51530,7 +51530,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
@@ -51717,7 +51717,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -52144,7 +52144,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52327,7 +52327,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52647,7 +52647,7 @@
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L853" t="inlineStr">
@@ -52712,7 +52712,7 @@
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
@@ -52762,7 +52762,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -52884,7 +52884,7 @@
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -52945,7 +52945,7 @@
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -53006,7 +53006,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -53067,7 +53067,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -53128,7 +53128,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53189,7 +53189,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -53204,7 +53204,7 @@
       </c>
       <c r="K862" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L862" t="inlineStr">
@@ -53254,7 +53254,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -53315,7 +53315,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -53437,7 +53437,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53498,7 +53498,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -53559,7 +53559,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -53620,7 +53620,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53681,7 +53681,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -53742,7 +53742,7 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -53803,7 +53803,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -53864,7 +53864,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -53925,7 +53925,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -53986,7 +53986,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -54047,7 +54047,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -54108,7 +54108,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -54169,7 +54169,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -54230,7 +54230,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -54291,7 +54291,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -54352,7 +54352,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -54413,7 +54413,7 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -54474,7 +54474,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54535,7 +54535,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -54596,7 +54596,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -54657,7 +54657,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54718,7 +54718,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -54779,7 +54779,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -54840,7 +54840,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -54901,7 +54901,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -54962,7 +54962,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -55023,7 +55023,7 @@
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -55084,7 +55084,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -55145,7 +55145,7 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55267,7 +55267,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -55328,7 +55328,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -55389,7 +55389,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -55450,7 +55450,7 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -55572,7 +55572,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -55633,7 +55633,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -55694,7 +55694,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -55755,7 +55755,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -55877,7 +55877,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -55999,7 +55999,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -56060,7 +56060,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -56121,7 +56121,7 @@
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
@@ -56182,7 +56182,7 @@
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -56243,7 +56243,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -56304,7 +56304,7 @@
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
@@ -56365,7 +56365,7 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -56380,7 +56380,7 @@
       </c>
       <c r="K914" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L914" t="inlineStr">
@@ -56430,7 +56430,7 @@
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
@@ -56445,7 +56445,7 @@
       </c>
       <c r="K915" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L915" t="inlineStr">
@@ -56495,7 +56495,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56556,7 +56556,7 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -56617,7 +56617,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -56678,7 +56678,7 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
